--- a/certs/GH200 Certs.xlsx
+++ b/certs/GH200 Certs.xlsx
@@ -7,7 +7,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,12 @@
     <sheet name="Sheet9" sheetId="9" r:id="rId9"/>
     <sheet name="Sheet10" sheetId="10" r:id="rId10"/>
     <sheet name="Sheet11" sheetId="11" r:id="rId11"/>
+    <sheet name="Sheet12" sheetId="12" r:id="rId12"/>
+    <sheet name="Sheet15" sheetId="13" r:id="rId13"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">KB!$A$1:$C$53</definedName>
+  </definedNames>
   <calcPr/>
 </workbook>
 </file>
@@ -632,6 +637,33 @@
     <t xml:space="preserve">GitHub Action Not Available to Enterprise Users Due to Distribution Configuration </t>
   </si>
   <si>
+    <t>Enterprise Organization Actions Policy Blocking Third-Party</t>
+  </si>
+  <si>
+    <t>Reusable Workflow Fails When Called from Another Repository</t>
+  </si>
+  <si>
+    <t>Workflow Template Not Available When Creating a New Repos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preinstalled Software Missing or Incorrect Version on GitHub-Hosted Runner </t>
+  </si>
+  <si>
+    <t xml:space="preserve">setup-* Action Fails to Install or Configure the Required Tool Version </t>
+  </si>
+  <si>
+    <t>GitHub Actions Environment Protection Issues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required Reviewers / Approval Gates in GitHub Actions </t>
+  </si>
+  <si>
+    <t>OpenID Connect (OIDC) in GitHub Actions</t>
+  </si>
+  <si>
+    <t>KB GITHUB_TOKEN in GitHub Actions</t>
+  </si>
+  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -917,6 +949,12 @@
     <t>Enterprise/org action policies</t>
   </si>
   <si>
+    <t>w3</t>
+  </si>
+  <si>
+    <t>21 Aug Main sent</t>
+  </si>
+  <si>
     <t>Reusable components</t>
   </si>
   <si>
@@ -971,6 +1009,9 @@
     <t>Script injection</t>
   </si>
   <si>
+    <t>${{github.even.issues.output}}</t>
+  </si>
+  <si>
     <t>Least privilege</t>
   </si>
   <si>
@@ -989,6 +1030,9 @@
     <t>Artifact attestations / provenance</t>
   </si>
   <si>
+    <t>w4</t>
+  </si>
+  <si>
     <t>Artifact retention</t>
   </si>
   <si>
@@ -1389,13 +1433,190 @@
   </si>
   <si>
     <t>Review is completed and changes are approved.</t>
+  </si>
+  <si>
+    <t>Trigger</t>
+  </si>
+  <si>
+    <t>Primary escalation</t>
+  </si>
+  <si>
+    <t>Management/vendor escalation</t>
+  </si>
+  <si>
+    <t>P1/critical impact</t>
+  </si>
+  <si>
+    <t>L1/L2 → Team Lead/Major Incident Manager</t>
+  </si>
+  <si>
+    <t>SDM → Customer Incident Manager → Microsoft/GitHub Support</t>
+  </si>
+  <si>
+    <t>Technical complexity or product defect</t>
+  </si>
+  <si>
+    <t>L1 → L2</t>
+  </si>
+  <si>
+    <t>Team Lead → authorized vendor support contact</t>
+  </si>
+  <si>
+    <t>SLA breach risk or complaint</t>
+  </si>
+  <si>
+    <t>Engineer → Team Lead</t>
+  </si>
+  <si>
+    <t>SDM → customer service owner/account leadership</t>
+  </si>
+  <si>
+    <t>Security or data concern</t>
+  </si>
+  <si>
+    <t>Stop unsafe action; notify Team Lead/SOC</t>
+  </si>
+  <si>
+    <t>Customer security lead and vendor security path as authorized</t>
+  </si>
+  <si>
+    <t>Access delayed or blocked</t>
+  </si>
+  <si>
+    <t>Onboarding owner → Team Lead</t>
+  </si>
+  <si>
+    <t>Team Lead → SDM → Customer Service Owner</t>
+  </si>
+  <si>
+    <t>KT session missed or incomplete</t>
+  </si>
+  <si>
+    <t>SDM → customer stakeholder</t>
+  </si>
+  <si>
+    <t>Customer unresponsive on required inputs</t>
+  </si>
+  <si>
+    <t>SDM → Customer Service Owner</t>
+  </si>
+  <si>
+    <t>Readiness review fails or open risks unresolved</t>
+  </si>
+  <si>
+    <t>Team Lead → SDM</t>
+  </si>
+  <si>
+    <t>SDM → Customer Service Owner (go/no-go decision)</t>
+  </si>
+  <si>
+    <t>Vendor case delayed beyond SLA</t>
+  </si>
+  <si>
+    <t>L2 → Team Lead</t>
+  </si>
+  <si>
+    <t>SDM → Microsoft/GitHub Support account team</t>
+  </si>
+  <si>
+    <t>Scope creep or out-of-contract request</t>
+  </si>
+  <si>
+    <t>SDM → Customer Service Owner (contract review)</t>
+  </si>
+  <si>
+    <t>Major incident during hypercare</t>
+  </si>
+  <si>
+    <t>Risk</t>
+  </si>
+  <si>
+    <t>Mitigation</t>
+  </si>
+  <si>
+    <t>Incomplete discovery</t>
+  </si>
+  <si>
+    <t>Mandatory questionnaire and architecture review</t>
+  </si>
+  <si>
+    <t>Delayed access</t>
+  </si>
+  <si>
+    <t>Early request, aged-item escalation</t>
+  </si>
+  <si>
+    <t>Premature go-live</t>
+  </si>
+  <si>
+    <t>Formal go/no-go criteria</t>
+  </si>
+  <si>
+    <t>Scope creep during execution</t>
+  </si>
+  <si>
+    <t>Change control with sign-off before adding scope</t>
+  </si>
+  <si>
+    <t>Vendor non-responsiveness</t>
+  </si>
+  <si>
+    <t>Escalation matrix with defined SLA timelines</t>
+  </si>
+  <si>
+    <t>Undocumented dependencies</t>
+  </si>
+  <si>
+    <t>Dependency mapping validated by architecture team</t>
+  </si>
+  <si>
+    <t>Credential/access misuse</t>
+  </si>
+  <si>
+    <t>Least-privilege access with periodic review</t>
+  </si>
+  <si>
+    <t>Miscommunication across teams</t>
+  </si>
+  <si>
+    <t>Single point of contact and daily sync updates</t>
+  </si>
+  <si>
+    <t>Testing gaps before deployment</t>
+  </si>
+  <si>
+    <t>Mandatory UAT sign-off before go-live</t>
+  </si>
+  <si>
+    <t>Resource unavailability</t>
+  </si>
+  <si>
+    <t>Backup owner assigned for critical tasks</t>
+  </si>
+  <si>
+    <t>Data loss during migration</t>
+  </si>
+  <si>
+    <t>Verified backup and rollback plan in place</t>
+  </si>
+  <si>
+    <t>Compliance/audit gaps</t>
+  </si>
+  <si>
+    <t>Evidence collection mapped to audit checklist</t>
+  </si>
+  <si>
+    <t>Unplanned downtime impact</t>
+  </si>
+  <si>
+    <t>Change freeze window and stakeholder notification</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1408,8 +1629,14 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1421,8 +1648,28 @@
         <fgColor rgb="FFC0504D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4F81BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF093367"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF225490"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border/>
     <border>
       <left style="thin">
@@ -1449,34 +1696,22 @@
         <color rgb="FF000000"/>
       </top>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2094,138 +2329,138 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -2247,162 +2482,432 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>453</v>
+        <v>466</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultColWidth="8.816406" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="40" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.17969" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.816406"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>472</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="28.08984" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.72656" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>525</v>
       </c>
     </row>
   </sheetData>
@@ -3513,61 +4018,161 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="6">
+      <c r="A47" s="2">
         <v>46248</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="3" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="6">
+      <c r="A48" s="2">
         <v>46248</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="3" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="6">
+      <c r="A49" s="2">
         <v>46248</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="3" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6">
+      <c r="A50" s="4">
         <v>46248</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="5" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6">
+      <c r="A51" s="2">
         <v>46248</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2">
+        <v>46252</v>
+      </c>
+      <c r="B57" t="s">
+        <v>206</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2">
+        <v>46252</v>
+      </c>
+      <c r="B58" t="s">
+        <v>207</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2">
+        <v>46252</v>
+      </c>
+      <c r="B59" t="s">
+        <v>208</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2">
+        <v>46252</v>
+      </c>
+      <c r="B60" t="s">
+        <v>209</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>151</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C53"/>
 </worksheet>
 </file>
 
@@ -3585,38 +4190,38 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B2" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C2" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="D2" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="E2" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B5" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C5" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="E5" s="3">
         <v>5</v>
@@ -3627,16 +4232,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="B6" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C6" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E6" s="3">
         <v>2</v>
@@ -3647,16 +4252,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B7" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C7" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="E7" s="3">
         <v>3</v>
@@ -3667,16 +4272,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="B8" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="C8" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="E8" s="3">
         <v>5</v>
@@ -3687,16 +4292,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B9" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C9" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="E9" s="3">
         <v>3</v>
@@ -3707,16 +4312,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B10" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C10" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="E10" s="3">
         <v>3</v>
@@ -3727,16 +4332,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B11" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C11" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="E11" s="3">
         <v>0</v>
@@ -3747,16 +4352,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="B12" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C12" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="E12" s="3">
         <v>4</v>
@@ -3767,16 +4372,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="B13" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C13" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="E13" s="3">
         <v>1</v>
@@ -3787,16 +4392,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="B14" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C14" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="E14" s="3">
         <v>3</v>
@@ -3807,16 +4412,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="B15" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C15" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="E15" s="3">
         <v>3</v>
@@ -3827,16 +4432,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B16" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C16" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="E16" s="3">
         <v>0</v>
@@ -3847,16 +4452,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B17" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C17" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="E17" s="3">
         <v>5</v>
@@ -3867,16 +4472,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="B18" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C18" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="E18" s="3">
         <v>4</v>
@@ -3887,16 +4492,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="B19" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C19" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="E19" s="3">
         <v>1</v>
@@ -3907,22 +4512,22 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -3934,46 +4539,47 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="50.26953" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="s">
-        <v>257</v>
+      <c r="A2" s="6" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11">
@@ -3983,12 +4589,12 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14">
@@ -3997,8 +4603,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="s">
-        <v>266</v>
+      <c r="A15" s="7" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="16">
@@ -4008,67 +4614,67 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="s">
-        <v>272</v>
+      <c r="A23" s="6" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33">
@@ -4078,249 +4684,336 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="s">
-        <v>282</v>
+      <c r="A37" s="6" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="s">
-        <v>284</v>
+      <c r="A41" s="3" t="s">
+        <v>293</v>
       </c>
       <c r="C41" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="s">
-        <v>285</v>
+      <c r="A42" s="3" t="s">
+        <v>294</v>
       </c>
       <c r="C42" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="s">
+      <c r="A43" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="s">
-        <v>286</v>
+      <c r="A44" s="3" t="s">
+        <v>295</v>
       </c>
       <c r="C44" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="s">
-        <v>287</v>
+      <c r="A45" s="3" t="s">
+        <v>296</v>
       </c>
       <c r="C45" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="s">
-        <v>288</v>
+      <c r="A46" s="3" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="s">
-        <v>289</v>
+      <c r="A47" s="3" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="s">
-        <v>290</v>
+      <c r="A48" s="3" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="s">
-        <v>291</v>
+      <c r="A49" s="3" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="s">
-        <v>292</v>
+      <c r="A50" s="3" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="s">
-        <v>293</v>
+      <c r="A52" s="6" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="s">
-        <v>295</v>
+      <c r="A56" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C56" t="s">
+        <v>305</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="s">
-        <v>296</v>
+      <c r="A57" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C57" t="s">
+        <v>305</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="s">
-        <v>297</v>
+      <c r="A58" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C58" t="s">
+        <v>305</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="s">
-        <v>298</v>
+      <c r="A59" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="s">
+      <c r="A60" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="D60" s="3" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="s">
+      <c r="A61" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="C61" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="s">
-        <v>299</v>
+      <c r="A62" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C62" t="s">
+        <v>19</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="s">
-        <v>300</v>
+      <c r="A63" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="s">
-        <v>301</v>
+      <c r="A64" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C64" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="s">
-        <v>302</v>
+      <c r="A65" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C65" t="s">
+        <v>305</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="s">
-        <v>303</v>
+      <c r="A66" s="3" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="s">
-        <v>304</v>
+      <c r="A67" s="3" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="s">
-        <v>306</v>
+      <c r="A70" s="6" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>308</v>
+        <v>319</v>
+      </c>
+      <c r="C74" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>309</v>
+        <v>320</v>
+      </c>
+      <c r="C75" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>310</v>
+        <v>321</v>
+      </c>
+      <c r="C76" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>311</v>
+        <v>322</v>
+      </c>
+      <c r="C77" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
         <v>126</v>
       </c>
+      <c r="C79" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>313</v>
+        <v>324</v>
+      </c>
+      <c r="C80" t="s">
+        <v>305</v>
+      </c>
+      <c r="D80" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="s">
-        <v>315</v>
+      <c r="A82" s="8" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="s">
-        <v>316</v>
+      <c r="A83" s="8" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>319</v>
+        <v>331</v>
+      </c>
+      <c r="C86" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
         <v>23</v>
       </c>
+      <c r="C87" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>320</v>
+        <v>333</v>
+      </c>
+      <c r="C88" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>321</v>
+        <v>334</v>
+      </c>
+      <c r="C89" t="s">
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -4338,101 +5031,101 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>340</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -4449,370 +5142,370 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>350</v>
-      </c>
       <c r="C11" s="3" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>352</v>
-      </c>
       <c r="F13" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -4829,42 +5522,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
